--- a/backend/src/workflows/claim-status/portals/availity/config/Payer_mapping_ava.xlsx
+++ b/backend/src/workflows/claim-status/portals/availity/config/Payer_mapping_ava.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alamelu\Documents\Repos\claim-status-check\backend\src\scrapers\availity\config\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alamelu\Documents\Repos\claim-status-check\backend\src\workflows\claim-status\portals\availity\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31F17329-0A11-4F70-A1B4-7FDD1D18E3BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AB3567A-2312-41F9-8621-A79722FF7FF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{4DE94660-A54E-46F6-AD6A-893CA67AF137}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="15">
   <si>
     <t xml:space="preserve">Payer name in excel </t>
   </si>
@@ -64,6 +64,12 @@
   </si>
   <si>
     <t>WELLCARE</t>
+  </si>
+  <si>
+    <t>Humana gold Plus</t>
+  </si>
+  <si>
+    <t>HUMANA</t>
   </si>
 </sst>
 </file>
@@ -415,7 +421,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B88755D1-98D7-4BD5-87AA-1A7D67B6D9D9}">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="47" customWidth="1"/>
@@ -478,6 +484,22 @@
         <v>12</v>
       </c>
     </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" t="s">
+        <v>14</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/backend/src/workflows/claim-status/portals/availity/config/Payer_mapping_ava.xlsx
+++ b/backend/src/workflows/claim-status/portals/availity/config/Payer_mapping_ava.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alamelu\Documents\Repos\claim-status-check\backend\src\workflows\claim-status\portals\availity\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AB3567A-2312-41F9-8621-A79722FF7FF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95E6A7B3-AF72-488D-92EA-A07354045DF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{4DE94660-A54E-46F6-AD6A-893CA67AF137}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="17">
   <si>
     <t xml:space="preserve">Payer name in excel </t>
   </si>
@@ -70,19 +70,31 @@
   </si>
   <si>
     <t>HUMANA</t>
+  </si>
+  <si>
+    <t>1 - BLUE CROSS OF CALIFORNIA</t>
+  </si>
+  <si>
+    <t>ANTHEM - CA</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF242424"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -105,8 +117,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -421,7 +434,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B88755D1-98D7-4BD5-87AA-1A7D67B6D9D9}">
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="47" customWidth="1"/>
@@ -500,6 +513,14 @@
         <v>14</v>
       </c>
     </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" t="s">
+        <v>16</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/backend/src/workflows/claim-status/portals/availity/config/Payer_mapping_ava.xlsx
+++ b/backend/src/workflows/claim-status/portals/availity/config/Payer_mapping_ava.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alamelu\Documents\Repos\claim-status-check\backend\src\workflows\claim-status\portals\availity\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95E6A7B3-AF72-488D-92EA-A07354045DF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85C4620A-B206-4DF3-A29C-8DDEDE533410}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{4DE94660-A54E-46F6-AD6A-893CA67AF137}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="25">
   <si>
     <t xml:space="preserve">Payer name in excel </t>
   </si>
@@ -76,13 +76,37 @@
   </si>
   <si>
     <t>ANTHEM - CA</t>
+  </si>
+  <si>
+    <t>MOLINA HEALTHCARE CALIFORNIA</t>
+  </si>
+  <si>
+    <t>2 - MOLINA (MCAL)</t>
+  </si>
+  <si>
+    <t>2 - MOLINA</t>
+  </si>
+  <si>
+    <t>1 - MOLINA (MCAL)</t>
+  </si>
+  <si>
+    <t>1 - MOLINA</t>
+  </si>
+  <si>
+    <t>2 - MOLINA MEDICAL GROUP</t>
+  </si>
+  <si>
+    <t>2 - MOLINA ADVANTAGE(MCARE)</t>
+  </si>
+  <si>
+    <t>2 - MOLINA HEALTHCARE</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -95,6 +119,13 @@
       <color rgb="FF242424"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -117,9 +148,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -434,11 +469,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B88755D1-98D7-4BD5-87AA-1A7D67B6D9D9}">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="47" customWidth="1"/>
     <col min="2" max="2" width="34.140625" customWidth="1"/>
+    <col min="6" max="8" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -521,6 +557,65 @@
         <v>16</v>
       </c>
     </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="3"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/backend/src/workflows/claim-status/portals/availity/config/Payer_mapping_ava.xlsx
+++ b/backend/src/workflows/claim-status/portals/availity/config/Payer_mapping_ava.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alamelu\Documents\Repos\claim-status-check\backend\src\workflows\claim-status\portals\availity\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85C4620A-B206-4DF3-A29C-8DDEDE533410}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFDF1E1F-C647-4451-B6BF-ACE1369613E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{4DE94660-A54E-46F6-AD6A-893CA67AF137}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="52">
   <si>
     <t xml:space="preserve">Payer name in excel </t>
   </si>
@@ -100,13 +100,94 @@
   </si>
   <si>
     <t>2 - MOLINA HEALTHCARE</t>
+  </si>
+  <si>
+    <t>1 - HEALTH NET IFP ENHANCED CARE PPO</t>
+  </si>
+  <si>
+    <t>1 - HEALTH NET</t>
+  </si>
+  <si>
+    <t>1 - HEALTH NET COMMERCIAL</t>
+  </si>
+  <si>
+    <t>1 - HEALTH NET COMMERCIAL CLAIMS</t>
+  </si>
+  <si>
+    <t>1 - HEALTH NET HMO DIRECT NETWORK</t>
+  </si>
+  <si>
+    <t>1 - HEALTH NET PPO</t>
+  </si>
+  <si>
+    <t>1 - HEALTH NET MEDI-CAL</t>
+  </si>
+  <si>
+    <t>1 - HEALTH NET - COMM</t>
+  </si>
+  <si>
+    <t>2 - HEALTH NET</t>
+  </si>
+  <si>
+    <t>1 - HEALTH NET FEDERAL SERVICES</t>
+  </si>
+  <si>
+    <t>2 - HEALTH NET IFP ENHANCED CARE PPO</t>
+  </si>
+  <si>
+    <t>2 - HEALTH NET - COMM</t>
+  </si>
+  <si>
+    <t>2 - HEALTH NET HMO DIRECT NETWORK</t>
+  </si>
+  <si>
+    <t>1 - HEALTH NET FEDERAL SERVICES, LLC</t>
+  </si>
+  <si>
+    <t>HEALTH NET</t>
+  </si>
+  <si>
+    <t>1 - HUMANA</t>
+  </si>
+  <si>
+    <t>1 - HUMANA CHOICE CARE PPO</t>
+  </si>
+  <si>
+    <t>2 - HUMANA CHOICE CARE PPO</t>
+  </si>
+  <si>
+    <t>2 - HUMANA</t>
+  </si>
+  <si>
+    <t>TRIWEST - TRICARE</t>
+  </si>
+  <si>
+    <t>1 - TRIWEST HEALTHCARE ALLIANCE</t>
+  </si>
+  <si>
+    <t>1 - TRICARE WEST REGION CLAIMS</t>
+  </si>
+  <si>
+    <t>1 - TRICARE WEST CLAIM</t>
+  </si>
+  <si>
+    <t>1 - TRICARE WEST</t>
+  </si>
+  <si>
+    <t>3 - TRICARE WEST CLAIM</t>
+  </si>
+  <si>
+    <t>1 - TRIWEST-TRICARE WEST REGION</t>
+  </si>
+  <si>
+    <t>2 - TRIWEST HEALTHCARE ALLIANCE</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -126,6 +207,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -148,13 +235,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -469,7 +559,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B88755D1-98D7-4BD5-87AA-1A7D67B6D9D9}">
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="47" customWidth="1"/>
@@ -614,7 +704,204 @@
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="3"/>
+      <c r="A18" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B18" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B19" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B21" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B23" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B24" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B25" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B26" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B28" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B29" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B30" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B31" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>40</v>
+      </c>
+      <c r="B32" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>41</v>
+      </c>
+      <c r="B33" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B34" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B35" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B36" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B37" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B38" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B39" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B40" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B41" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B42" t="s">
+        <v>44</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/backend/src/workflows/claim-status/portals/availity/config/Payer_mapping_ava.xlsx
+++ b/backend/src/workflows/claim-status/portals/availity/config/Payer_mapping_ava.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alamelu\Documents\Repos\claim-status-check\backend\src\workflows\claim-status\portals\availity\config\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vignesh\Desktop\Vignesh\claim-status\iehp-claim-status-check\backend\src\workflows\claim-status\portals\availity\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFDF1E1F-C647-4451-B6BF-ACE1369613E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12E4DAA4-4C88-456A-9406-21D8B717D799}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{4DE94660-A54E-46F6-AD6A-893CA67AF137}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{4DE94660-A54E-46F6-AD6A-893CA67AF137}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="charm" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="54">
   <si>
     <t xml:space="preserve">Payer name in excel </t>
   </si>
@@ -181,13 +182,19 @@
   </si>
   <si>
     <t>2 - TRIWEST HEALTHCARE ALLIANCE</t>
+  </si>
+  <si>
+    <t>Payer name in excel</t>
+  </si>
+  <si>
+    <t>Payer :  [ 99726 ] - Tricare | West Region</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -560,14 +567,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B88755D1-98D7-4BD5-87AA-1A7D67B6D9D9}">
   <dimension ref="A1:B42"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="47" customWidth="1"/>
     <col min="2" max="2" width="34.140625" customWidth="1"/>
     <col min="6" max="8" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -575,7 +582,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -583,7 +590,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -591,7 +598,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -599,7 +606,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -607,7 +614,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -615,7 +622,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -623,7 +630,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -631,7 +638,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -639,7 +646,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
         <v>15</v>
       </c>
@@ -647,7 +654,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2">
       <c r="A11" s="2" t="s">
         <v>18</v>
       </c>
@@ -655,7 +662,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2">
       <c r="A12" s="2" t="s">
         <v>19</v>
       </c>
@@ -663,7 +670,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2">
       <c r="A13" s="2" t="s">
         <v>20</v>
       </c>
@@ -671,7 +678,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2">
       <c r="A14" s="2" t="s">
         <v>21</v>
       </c>
@@ -679,7 +686,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2">
       <c r="A15" s="2" t="s">
         <v>22</v>
       </c>
@@ -687,7 +694,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2">
       <c r="A16" s="2" t="s">
         <v>23</v>
       </c>
@@ -695,7 +702,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2">
       <c r="A17" s="2" t="s">
         <v>24</v>
       </c>
@@ -703,7 +710,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2">
       <c r="A18" s="3" t="s">
         <v>26</v>
       </c>
@@ -711,7 +718,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2">
       <c r="A19" s="3" t="s">
         <v>33</v>
       </c>
@@ -719,7 +726,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2">
       <c r="A20" s="3" t="s">
         <v>27</v>
       </c>
@@ -727,7 +734,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2">
       <c r="A21" s="3" t="s">
         <v>34</v>
       </c>
@@ -735,7 +742,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2">
       <c r="A22" s="3" t="s">
         <v>29</v>
       </c>
@@ -743,7 +750,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2">
       <c r="A23" s="3" t="s">
         <v>25</v>
       </c>
@@ -751,7 +758,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2">
       <c r="A24" s="3" t="s">
         <v>35</v>
       </c>
@@ -759,7 +766,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2">
       <c r="A25" s="3" t="s">
         <v>36</v>
       </c>
@@ -767,7 +774,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2">
       <c r="A26" s="3" t="s">
         <v>32</v>
       </c>
@@ -775,7 +782,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2">
       <c r="A27" s="3" t="s">
         <v>37</v>
       </c>
@@ -783,7 +790,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2">
       <c r="A28" s="3" t="s">
         <v>31</v>
       </c>
@@ -791,7 +798,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2">
       <c r="A29" s="3" t="s">
         <v>30</v>
       </c>
@@ -799,7 +806,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2">
       <c r="A30" s="3" t="s">
         <v>28</v>
       </c>
@@ -807,7 +814,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2">
       <c r="A31" s="3" t="s">
         <v>38</v>
       </c>
@@ -815,7 +822,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2">
       <c r="A32" t="s">
         <v>40</v>
       </c>
@@ -823,7 +830,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2">
       <c r="A33" t="s">
         <v>41</v>
       </c>
@@ -831,7 +838,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2">
       <c r="A34" s="2" t="s">
         <v>42</v>
       </c>
@@ -839,7 +846,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="35" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" ht="18" customHeight="1">
       <c r="A35" s="2" t="s">
         <v>43</v>
       </c>
@@ -847,7 +854,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2">
       <c r="A36" s="4" t="s">
         <v>45</v>
       </c>
@@ -855,7 +862,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2">
       <c r="A37" s="4" t="s">
         <v>47</v>
       </c>
@@ -863,7 +870,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2">
       <c r="A38" s="4" t="s">
         <v>46</v>
       </c>
@@ -871,7 +878,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2">
       <c r="A39" s="4" t="s">
         <v>48</v>
       </c>
@@ -879,7 +886,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2">
       <c r="A40" s="4" t="s">
         <v>49</v>
       </c>
@@ -887,7 +894,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2">
       <c r="A41" s="4" t="s">
         <v>50</v>
       </c>
@@ -895,11 +902,41 @@
         <v>44</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2">
       <c r="A42" s="4" t="s">
         <v>51</v>
       </c>
       <c r="B42" t="s">
+        <v>44</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12612F4C-44F3-404E-9712-43C40011520F}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="46.5703125" customWidth="1"/>
+    <col min="2" max="2" width="30.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B2" t="s">
         <v>44</v>
       </c>
     </row>

--- a/backend/src/workflows/claim-status/portals/availity/config/Payer_mapping_ava.xlsx
+++ b/backend/src/workflows/claim-status/portals/availity/config/Payer_mapping_ava.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alamelu\Documents\Repos\claim-status-check\backend\src\workflows\claim-status\portals\availity\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFDF1E1F-C647-4451-B6BF-ACE1369613E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C378D52F-6758-4263-863E-82CDF2DE5A02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{4DE94660-A54E-46F6-AD6A-893CA67AF137}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="80">
   <si>
     <t xml:space="preserve">Payer name in excel </t>
   </si>
@@ -181,13 +181,97 @@
   </si>
   <si>
     <t>2 - TRIWEST HEALTHCARE ALLIANCE</t>
+  </si>
+  <si>
+    <t>TRIWEST-VA CCN</t>
+  </si>
+  <si>
+    <t>1 - TRIWEST VA CCN</t>
+  </si>
+  <si>
+    <t>1 - TRIWEST VACC CLAIMS</t>
+  </si>
+  <si>
+    <t>1 - TRIWEST VA CCN CLAIMS</t>
+  </si>
+  <si>
+    <t>2 - TRIWEST VA CCN</t>
+  </si>
+  <si>
+    <t>2 - TRIWEST ALLIANCE VA CCN CLAIMS</t>
+  </si>
+  <si>
+    <t>1 - TRIWEST HEALTHCARE ALLIANCE (WPA-VA)</t>
+  </si>
+  <si>
+    <t>1 - AETNA</t>
+  </si>
+  <si>
+    <t>SCAN HEALTH PLAN</t>
+  </si>
+  <si>
+    <t>1 - SCAN</t>
+  </si>
+  <si>
+    <t>1 - VILLAGE HEALTH OP BY SCAN</t>
+  </si>
+  <si>
+    <t>1 - VILLAGE HEALTH</t>
+  </si>
+  <si>
+    <t>1 - SCAN HEALTH PLAN</t>
+  </si>
+  <si>
+    <t>PROVIDENCE HEALTH PLAN POWERED BY COLLECTIVE HEALTH</t>
+  </si>
+  <si>
+    <t>1 - PROVIDENCE HEALTH PLAN</t>
+  </si>
+  <si>
+    <t>2 - AETNA</t>
+  </si>
+  <si>
+    <t>1 - AETNA CHOICE POS</t>
+  </si>
+  <si>
+    <t>1 - AETNA GLOBAL BENEFITS</t>
+  </si>
+  <si>
+    <t>2 - AETNA CHOICE POS</t>
+  </si>
+  <si>
+    <t>2 - AETNA CHOICE POS II</t>
+  </si>
+  <si>
+    <t>2 - BLUE CROSS OF CALIFORNIA PPO</t>
+  </si>
+  <si>
+    <t>2 - BLUE CROSS PPO</t>
+  </si>
+  <si>
+    <t>1 - BLUE CROSS OF CALIFORNIA PPO</t>
+  </si>
+  <si>
+    <t>2 - BLUE CROSS OF CALIFORNIA</t>
+  </si>
+  <si>
+    <t>1 - AETNA MEDICARE</t>
+  </si>
+  <si>
+    <t>1 - AETNA CHOICE POS II</t>
+  </si>
+  <si>
+    <t>1 - AETNA SENIOR</t>
+  </si>
+  <si>
+    <t>1 - BLUE CROSS PPO</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -214,6 +298,13 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -223,7 +314,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -231,20 +322,39 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -559,15 +669,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B88755D1-98D7-4BD5-87AA-1A7D67B6D9D9}">
-  <dimension ref="A1:B42"/>
+  <dimension ref="A1:E67"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="47" customWidth="1"/>
-    <col min="2" max="2" width="34.140625" customWidth="1"/>
+    <col min="2" max="2" width="66" customWidth="1"/>
     <col min="6" max="8" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -575,7 +685,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -583,7 +693,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -591,316 +701,518 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E5" s="6"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="B8" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="B10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="B11" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="B12" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>2</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B13" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>7</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B14" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>9</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B15" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>11</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B16" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>13</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B17" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>40</v>
+      </c>
+      <c r="B18" t="s">
         <v>14</v>
       </c>
-      <c r="B9" t="s">
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>41</v>
+      </c>
+      <c r="B19" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B20" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B21" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>14</v>
+      </c>
+      <c r="B22" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B23" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B24" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="B25" t="s">
+        <v>16</v>
+      </c>
+      <c r="D25" s="1"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="B26" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="B27" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B28" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B29" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B30" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B31" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B32" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B33" t="s">
         <v>17</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B16" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B17" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B18" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B19" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B20" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B21" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B22" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B23" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B24" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B25" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B26" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B27" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B28" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B29" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B30" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B31" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>40</v>
-      </c>
-      <c r="B32" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>41</v>
-      </c>
-      <c r="B33" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="B34" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="B35" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" s="4" t="s">
+      <c r="A36" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B36" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B37" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B38" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B39" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B40" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B41" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B42" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B43" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B44" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B45" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B46" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B47" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B48" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B49" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B50" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B51" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" s="4" t="s">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B52" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="4" t="s">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B53" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" s="4" t="s">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B54" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="4" t="s">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B55" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" s="4" t="s">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B56" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" s="4" t="s">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B57" t="s">
         <v>44</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B58" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B59" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B60" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B61" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B62" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B63" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B64" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A65" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B65" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B66" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B67" t="s">
+        <v>65</v>
       </c>
     </row>
   </sheetData>

--- a/backend/src/workflows/claim-status/portals/availity/config/Payer_mapping_ava.xlsx
+++ b/backend/src/workflows/claim-status/portals/availity/config/Payer_mapping_ava.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vignesh\Desktop\Vignesh\claim-status\iehp-claim-status-check\backend\src\workflows\claim-status\portals\availity\config\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hayagriva\Documents\Github Pages\iehp-claim-status-check\backend\src\workflows\claim-status\portals\availity\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12E4DAA4-4C88-456A-9406-21D8B717D799}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA617AD1-9409-4260-AF24-3EF2771DA95B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{4DE94660-A54E-46F6-AD6A-893CA67AF137}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{4DE94660-A54E-46F6-AD6A-893CA67AF137}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="63">
   <si>
     <t xml:space="preserve">Payer name in excel </t>
   </si>
@@ -185,6 +185,33 @@
   </si>
   <si>
     <t>Payer name in excel</t>
+  </si>
+  <si>
+    <t>Aetna [ 60054 ]</t>
+  </si>
+  <si>
+    <t>1 - AETNA</t>
+  </si>
+  <si>
+    <t>1 - TRIWEST HEALTHCARE ALLIANCE (WPA-VA)</t>
+  </si>
+  <si>
+    <t>1 - TRIWEST VA CCN</t>
+  </si>
+  <si>
+    <t>TRIWEST-VA CCN</t>
+  </si>
+  <si>
+    <t>1 - TRIWEST VACC CLAIMS</t>
+  </si>
+  <si>
+    <t>1 - TRIWEST VA CCN CLAIMS</t>
+  </si>
+  <si>
+    <t>2 - TRIWEST VA CCN</t>
+  </si>
+  <si>
+    <t>2 - TRIWEST ALLIANCE VA CCN CLAIMS</t>
   </si>
   <si>
     <t>Payer :  [ 99726 ] - Tricare | West Region</t>
@@ -194,7 +221,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -249,8 +276,8 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -567,14 +594,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B88755D1-98D7-4BD5-87AA-1A7D67B6D9D9}">
   <dimension ref="A1:B42"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="47" customWidth="1"/>
-    <col min="2" max="2" width="34.140625" customWidth="1"/>
-    <col min="6" max="8" width="9.140625" customWidth="1"/>
+    <col min="2" max="2" width="34.1796875" customWidth="1"/>
+    <col min="6" max="8" width="9.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -582,7 +609,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -590,7 +617,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -598,7 +625,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -606,7 +633,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -614,7 +641,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -622,7 +649,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -630,7 +657,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -638,7 +665,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -646,7 +673,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>15</v>
       </c>
@@ -654,7 +681,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>18</v>
       </c>
@@ -662,7 +689,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>19</v>
       </c>
@@ -670,7 +697,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>20</v>
       </c>
@@ -678,7 +705,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>21</v>
       </c>
@@ -686,7 +713,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
         <v>22</v>
       </c>
@@ -694,7 +721,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>23</v>
       </c>
@@ -702,7 +729,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
         <v>24</v>
       </c>
@@ -710,7 +737,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
         <v>26</v>
       </c>
@@ -718,7 +745,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
         <v>33</v>
       </c>
@@ -726,7 +753,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" s="3" t="s">
         <v>27</v>
       </c>
@@ -734,7 +761,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" s="3" t="s">
         <v>34</v>
       </c>
@@ -742,7 +769,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" s="3" t="s">
         <v>29</v>
       </c>
@@ -750,7 +777,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" s="3" t="s">
         <v>25</v>
       </c>
@@ -758,7 +785,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" s="3" t="s">
         <v>35</v>
       </c>
@@ -766,7 +793,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" s="3" t="s">
         <v>36</v>
       </c>
@@ -774,7 +801,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" s="3" t="s">
         <v>32</v>
       </c>
@@ -782,7 +809,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" s="3" t="s">
         <v>37</v>
       </c>
@@ -790,7 +817,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" s="3" t="s">
         <v>31</v>
       </c>
@@ -798,7 +825,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="29" spans="1:2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" s="3" t="s">
         <v>30</v>
       </c>
@@ -806,7 +833,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="30" spans="1:2">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" s="3" t="s">
         <v>28</v>
       </c>
@@ -814,7 +841,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="31" spans="1:2">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" s="3" t="s">
         <v>38</v>
       </c>
@@ -822,7 +849,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="32" spans="1:2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>40</v>
       </c>
@@ -830,7 +857,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="33" spans="1:2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>41</v>
       </c>
@@ -838,7 +865,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="34" spans="1:2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
         <v>42</v>
       </c>
@@ -846,7 +873,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="35" spans="1:2" ht="18" customHeight="1">
+    <row r="35" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
         <v>43</v>
       </c>
@@ -854,56 +881,56 @@
         <v>14</v>
       </c>
     </row>
-    <row r="36" spans="1:2">
-      <c r="A36" s="4" t="s">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A36" s="2" t="s">
         <v>45</v>
       </c>
       <c r="B36" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="37" spans="1:2">
-      <c r="A37" s="4" t="s">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A37" s="2" t="s">
         <v>47</v>
       </c>
       <c r="B37" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="38" spans="1:2">
-      <c r="A38" s="4" t="s">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A38" s="2" t="s">
         <v>46</v>
       </c>
       <c r="B38" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="39" spans="1:2">
-      <c r="A39" s="4" t="s">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A39" s="2" t="s">
         <v>48</v>
       </c>
       <c r="B39" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="40" spans="1:2">
-      <c r="A40" s="4" t="s">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A40" s="2" t="s">
         <v>49</v>
       </c>
       <c r="B40" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="41" spans="1:2">
-      <c r="A41" s="4" t="s">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A41" s="2" t="s">
         <v>50</v>
       </c>
       <c r="B41" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="42" spans="1:2">
-      <c r="A42" s="4" t="s">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A42" s="2" t="s">
         <v>51</v>
       </c>
       <c r="B42" t="s">
@@ -917,14 +944,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12612F4C-44F3-404E-9712-43C40011520F}">
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:B51"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="46.5703125" customWidth="1"/>
-    <col min="2" max="2" width="30.140625" customWidth="1"/>
+    <col min="1" max="1" width="46.54296875" customWidth="1"/>
+    <col min="2" max="2" width="31.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>52</v>
       </c>
@@ -932,12 +959,404 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B20" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B21" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B22" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B23" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A24" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B24" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A25" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B25" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A26" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B26" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A27" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A28" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B28" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A29" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B29" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A30" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B30" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A31" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B31" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A32" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>40</v>
+      </c>
+      <c r="B33" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>41</v>
+      </c>
+      <c r="B34" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A35" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B35" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B36" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B37" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A38" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B38" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A39" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B39" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A40" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B40" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A41" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B41" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A42" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B42" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A43" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B43" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A44" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B44" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A45" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B45" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A46" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B46" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A47" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B47" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A48" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B48" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A49" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B49" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
+        <v>62</v>
+      </c>
+      <c r="B50" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
         <v>53</v>
       </c>
-      <c r="B2" t="s">
-        <v>44</v>
+      <c r="B51" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
